--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,12 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>90935</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92917</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1884,12 +1879,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1898,7 +1893,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flymossgruvan (Flymossgruvan), Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>92917</v>
+        <v>92920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>92920</v>
+        <v>92923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>92923</v>
+        <v>92924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>92924</v>
+        <v>92941</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>92957</v>
+        <v>92959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>92959</v>
+        <v>93046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -1862,7 +1862,7 @@
         <v>112366407</v>
       </c>
       <c r="B13" t="n">
-        <v>93046</v>
+        <v>92959</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112366344</v>
+        <v>112371013</v>
       </c>
       <c r="B2" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flymossgruvan (Flymossgruvan), Gstr</t>
+          <t>Körbergsklack_östra, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578469</v>
+        <v>578522</v>
       </c>
       <c r="R2" t="n">
-        <v>6711594</v>
+        <v>6711578</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,19 +743,9 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,65 +760,63 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112371080</v>
+        <v>112366407</v>
       </c>
       <c r="B3" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Körbergsklack_östra, Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578489</v>
+        <v>578480</v>
       </c>
       <c r="R3" t="n">
-        <v>6711587</v>
+        <v>6711593</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,92 +843,89 @@
           <t>2023-09-28</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-28</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112365939</v>
+        <v>112366192</v>
       </c>
       <c r="B4" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flymossgruvan (Flymossgruvan), Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578480</v>
+        <v>578518</v>
       </c>
       <c r="R4" t="n">
-        <v>6711580</v>
+        <v>6711506</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +954,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +964,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,27 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112371077</v>
+        <v>112365914</v>
       </c>
       <c r="B5" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,19 +1020,20 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Körbergsklack_östra, Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578470</v>
+        <v>578482</v>
       </c>
       <c r="R5" t="n">
-        <v>6711588</v>
+        <v>6711589</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,9 +1060,19 @@
           <t>2023-09-28</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1087,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
+          <t>Annelie Hilmerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112365929</v>
+        <v>112365923</v>
       </c>
       <c r="B6" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,11 +1131,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Flymossgruvan (Flymossgruvan), Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578487</v>
+        <v>578497</v>
       </c>
       <c r="R6" t="n">
         <v>6711585</v>
@@ -1236,15 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112365914</v>
+        <v>112365929</v>
       </c>
       <c r="B7" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,14 +1239,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flymossgruvan (Flymossgruvan), Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578482</v>
+        <v>578487</v>
       </c>
       <c r="R7" t="n">
-        <v>6711589</v>
+        <v>6711585</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1312,7 +1278,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1288,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,15 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112371076</v>
+        <v>112365939</v>
       </c>
       <c r="B8" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,20 +1343,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Körbergsklack_östra, Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578476</v>
+        <v>578480</v>
       </c>
       <c r="R8" t="n">
-        <v>6711592</v>
+        <v>6711580</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,9 +1393,19 @@
           <t>2023-09-28</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,27 +1420,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112371078</v>
+        <v>112366344</v>
       </c>
       <c r="B9" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,20 +1460,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Körbergsklack_östra, Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>578466</v>
+        <v>578470</v>
       </c>
       <c r="R9" t="n">
-        <v>6711623</v>
+        <v>6711594</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,9 +1510,19 @@
           <t>2023-09-28</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,27 +1537,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112371079</v>
+        <v>112366413</v>
       </c>
       <c r="B10" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,20 +1577,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Körbergsklack_östra, Gstr</t>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>578476</v>
+        <v>578533</v>
       </c>
       <c r="R10" t="n">
-        <v>6711594</v>
+        <v>6711607</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1626,9 +1627,19 @@
           <t>2023-09-28</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1643,49 +1654,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112371013</v>
+        <v>112371076</v>
       </c>
       <c r="B11" t="n">
-        <v>90957</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>578522</v>
+        <v>578476</v>
       </c>
       <c r="R11" t="n">
-        <v>6711578</v>
+        <v>6711592</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1757,15 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112371081</v>
+        <v>112371077</v>
       </c>
       <c r="B12" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>578491</v>
+        <v>578470</v>
       </c>
       <c r="R12" t="n">
-        <v>6711589</v>
+        <v>6711588</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1859,51 +1860,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112366407</v>
+        <v>112371078</v>
       </c>
       <c r="B13" t="n">
-        <v>93046</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
+          <t>Körbergsklack_östra, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>578480</v>
+        <v>578466</v>
       </c>
       <c r="R13" t="n">
-        <v>6711593</v>
+        <v>6711623</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1930,55 +1928,39 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112365923</v>
+        <v>112371079</v>
       </c>
       <c r="B14" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2004,20 +1986,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flymossgruvan (Flymossgruvan), Gstr</t>
+          <t>Körbergsklack_östra, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>578497</v>
+        <v>578476</v>
       </c>
       <c r="R14" t="n">
-        <v>6711584</v>
+        <v>6711594</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,19 +2025,9 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,66 +2042,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112366298</v>
+        <v>112371080</v>
       </c>
       <c r="B15" t="n">
-        <v>103903</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Flymossgruvan (Flymossgruvan), Gstr</t>
+          <t>Körbergsklack_östra, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>578510</v>
+        <v>578489</v>
       </c>
       <c r="R15" t="n">
-        <v>6711540</v>
+        <v>6711587</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2157,19 +2122,9 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,27 +2139,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112388809</v>
+        <v>112371081</v>
       </c>
       <c r="B16" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2232,17 +2182,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Körbergsklack, Gstr</t>
+          <t>Körbergsklack_östra, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>578496</v>
+        <v>578491</v>
       </c>
       <c r="R16" t="n">
-        <v>6711520</v>
+        <v>6711589</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2286,27 +2236,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss, fanny westling, Bo karlstens, Annelie Hilmerby, FREDRIK Månsson, Maj-Lis Koivisto, Stephen Hinton</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112388811</v>
+        <v>112388809</v>
       </c>
       <c r="B17" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,10 +2283,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>578490</v>
+        <v>578496</v>
       </c>
       <c r="R17" t="n">
-        <v>6711517</v>
+        <v>6711519</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2403,12 +2348,7 @@
         <v>112388810</v>
       </c>
       <c r="B18" t="n">
-        <v>96844</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,10 +2380,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>578497</v>
+        <v>578496</v>
       </c>
       <c r="R18" t="n">
-        <v>6711525</v>
+        <v>6711524</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,6 +2439,211 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112388811</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Körbergsklack, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>578491</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6711516</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>fanny westling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112366298</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Flymossgruvan, Flymossgruvan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>578510</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6711540</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annelie Hilmerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38738-2023 artfynd.xlsx
+++ b/artfynd/A 38738-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112371013</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366407</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366192</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365914</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365923</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365929</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1429,6 +1464,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112365939</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366344</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1663,6 +1708,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366413</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112371076</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1857,6 +1912,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112371077</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1954,6 +2014,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112371078</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2051,6 +2116,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112371079</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2148,6 +2218,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112371080</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2245,6 +2320,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112371081</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2342,6 +2422,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388809</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2439,6 +2524,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388810</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2536,6 +2626,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112388811</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2644,8 +2739,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112366298</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>